--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-19).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-19).xlsx
@@ -915,54 +915,54 @@
   </si>
   <si>
     <t>215
-167</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 658.781,63</t>
-  </si>
-  <si>
-    <t>R$ 3.619,68
-R$ 3.702,61</t>
-  </si>
-  <si>
-    <t>(4.8%)
+175</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R$ 683.649,68</t>
+  </si>
+  <si>
+    <t>R$ 3.598,16
+R$ 3.675,45</t>
+  </si>
+  <si>
+    <t>(4.2%)
 (3.1%)</t>
   </si>
   <si>
-    <t>42.1</t>
-  </si>
-  <si>
-    <t>(6.2%)</t>
-  </si>
-  <si>
-    <t>(48.1%)</t>
-  </si>
-  <si>
-    <t>(85.9%)</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>25.7</t>
-  </si>
-  <si>
-    <t>75.3%</t>
-  </si>
-  <si>
-    <t>7.4%</t>
+    <t>41.7</t>
+  </si>
+  <si>
+    <t>(6.0%)</t>
+  </si>
+  <si>
+    <t>(41.4%)</t>
+  </si>
+  <si>
+    <t>(78.9%)</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>75.4%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>6.6</t>
+    <t>6.5</t>
   </si>
   <si>
     <t>11.2</t>
@@ -974,7 +974,7 @@
     <t>77.0%</t>
   </si>
   <si>
-    <t>-R$ 20.806,69</t>
+    <t>-R$ 21.182,99</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>7634.3199999999997</v>
+      </c>
+      <c r="P6" s="5">
+        <v>7634.3199999999997</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.33616166283372007</v>
+      </c>
+      <c r="R6" s="7">
+        <v>79</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.11267605633802824</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.28609133491915456</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.011728981756069958</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.018948838927370086</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-0.0069958424587913525</v>
+      </c>
+      <c r="X6" s="8">
+        <v>18.646237096774193</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>3.9565405063291141</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.6486564516129032</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>5.6508050000000001</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>12.611020967741934</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>1</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -5709,10 +5745,10 @@
         <v>-0.15476190476190477</v>
       </c>
       <c r="T34" s="6">
-        <v>0.23158044904377664</v>
+        <v>5.6807130575322446</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.11194121688163164</v>
+        <v>5.3646331763453841</v>
       </c>
       <c r="V34" s="6">
         <v>0.11192241406696743</v>
@@ -7882,7 +7918,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7918,11 +7954,21 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
+      <c r="O51" s="5">
+        <v>0</v>
+      </c>
+      <c r="P51" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-1</v>
+      </c>
       <c r="T51" s="6"/>
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
@@ -7936,7 +7982,9 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="6"/>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8809,7 +8857,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>8.5313719999999993</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -9505,7 +9555,7 @@
         <v>19633</v>
       </c>
       <c r="B64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C64" s="4">
         <v>44</v>
@@ -9539,25 +9589,61 @@
       <c t="s" r="N64" s="4">
         <v>52</v>
       </c>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
-      <c r="X64" s="8"/>
-      <c r="Y64" s="6"/>
-      <c r="Z64" s="6"/>
-      <c r="AA64" s="8"/>
-      <c r="AB64" s="8"/>
-      <c r="AC64" s="8"/>
-      <c r="AD64" s="8"/>
-      <c r="AE64" s="6"/>
+      <c r="O64" s="5">
+        <v>3458.3000000000002</v>
+      </c>
+      <c r="P64" s="5">
+        <v>3458.3000000000002</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>0.41228310185279726</v>
+      </c>
+      <c r="R64" s="7">
+        <v>35</v>
+      </c>
+      <c r="S64" s="6">
+        <v>-0.054054054054054057</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0.51088453864615557</v>
+      </c>
+      <c r="U64" s="6">
+        <v>0.21504843420177544</v>
+      </c>
+      <c r="V64" s="6">
+        <v>0.028865483040800392</v>
+      </c>
+      <c r="W64" s="6">
+        <v>-0.019889685683717431</v>
+      </c>
+      <c r="X64" s="8">
+        <v>27.78333125</v>
+      </c>
+      <c r="Y64" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z64" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="AA64" s="8">
+        <v>6.6873727272727272</v>
+      </c>
+      <c r="AB64" s="8">
+        <v>9.5320538461538469</v>
+      </c>
+      <c r="AC64" s="8">
+        <v>13.873716999999999</v>
+      </c>
+      <c r="AD64" s="8">
+        <v>18.11145625</v>
+      </c>
+      <c r="AE64" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF64" s="9"/>
-      <c r="AG64" s="5"/>
+      <c r="AG64" s="5">
+        <v>-260.19999999999999</v>
+      </c>
       <c r="AH64" s="10">
         <v>1</v>
       </c>
@@ -11006,7 +11092,7 @@
         <v>0.020997698867481839</v>
       </c>
       <c r="W76" s="6">
-        <v>-0.012929116094391553</v>
+        <v>-0.014116680954744394</v>
       </c>
       <c r="X76" s="8">
         <v>29.183823529411764</v>
@@ -11947,7 +12033,7 @@
         <v>19685</v>
       </c>
       <c r="B84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C84" s="4">
         <v>44</v>
@@ -11983,25 +12069,61 @@
       <c t="s" r="N84" s="4">
         <v>52</v>
       </c>
-      <c r="O84" s="5"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="7"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
-      <c r="V84" s="6"/>
-      <c r="W84" s="6"/>
-      <c r="X84" s="8"/>
-      <c r="Y84" s="6"/>
-      <c r="Z84" s="6"/>
-      <c r="AA84" s="8"/>
-      <c r="AB84" s="8"/>
-      <c r="AC84" s="8"/>
-      <c r="AD84" s="8"/>
-      <c r="AE84" s="6"/>
+      <c r="O84" s="5">
+        <v>2798.1999999999998</v>
+      </c>
+      <c r="P84" s="5">
+        <v>2798.1999999999998</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>-0.3301094060472578</v>
+      </c>
+      <c r="R84" s="7">
+        <v>29</v>
+      </c>
+      <c r="S84" s="6">
+        <v>-0.36956521739130432</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0</v>
+      </c>
+      <c r="U84" s="6">
+        <v>-0.29808090915588598</v>
+      </c>
+      <c r="V84" s="6">
+        <v>0.029845615038238869</v>
+      </c>
+      <c r="W84" s="6">
+        <v>-0.032909012936887999</v>
+      </c>
+      <c r="X84" s="8">
+        <v>29.39924090909091</v>
+      </c>
+      <c r="Y84" s="6">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="Z84" s="6">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AA84" s="8">
+        <v>4.7910714285714286</v>
+      </c>
+      <c r="AB84" s="8">
+        <v>6.8016649999999998</v>
+      </c>
+      <c r="AC84" s="8">
+        <v>12.006969</v>
+      </c>
+      <c r="AD84" s="8">
+        <v>17.956818181818182</v>
+      </c>
+      <c r="AE84" s="6">
+        <v>0.59090909090909094</v>
+      </c>
       <c r="AF84" s="9"/>
-      <c r="AG84" s="5"/>
+      <c r="AG84" s="5">
+        <v>0</v>
+      </c>
       <c r="AH84" s="10">
         <v>2</v>
       </c>
@@ -14185,7 +14307,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14221,25 +14343,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>2833.5</v>
+      </c>
+      <c r="P102" s="5">
+        <v>2833.5</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.057429128383907568</v>
+      </c>
+      <c r="R102" s="7">
+        <v>28</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.15151515151515149</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.000133545085583201</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.34129578260102345</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.017296982530439386</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.011448385389094758</v>
+      </c>
+      <c r="X102" s="8">
+        <v>127.26875</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>11.323455555555554</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>38.731818181818184</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>53.348483999999999</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>29.908329999999999</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -14618,7 +14776,9 @@
       <c r="AB105" s="8">
         <v>9.5861166666666673</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>17.330555</v>
+      </c>
       <c r="AD105" s="8">
         <v>23.563883333333333</v>
       </c>
@@ -16408,7 +16568,7 @@
         <v>0.023985071909703257</v>
       </c>
       <c r="W120" s="6">
-        <v>0.0040050973966866922</v>
+        <v>0.0051783077452110769</v>
       </c>
       <c r="X120" s="8">
         <v>26.896875000000001</v>
@@ -17450,7 +17610,7 @@
         <v>0.10631101403007644</v>
       </c>
       <c r="W128" s="6">
-        <v>0.06557991916136921</v>
+        <v>0.076957069646307649</v>
       </c>
       <c r="X128" s="8">
         <v>71.935900000000004</v>
@@ -20358,7 +20518,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20394,25 +20554,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>1508.8099999999999</v>
+      </c>
+      <c r="P151" s="5">
+        <v>1508.8099999999999</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.42446539872901079</v>
+      </c>
+      <c r="R151" s="7">
+        <v>19</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.38709677419354838</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.33345563722403748</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.0012651029619368908</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.067740139580198963</v>
+      </c>
+      <c r="W151" s="6">
+        <v>-0.0091615246452502307</v>
+      </c>
+      <c r="X151" s="8">
+        <v>22.120515384615388</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>3.2833333333333332</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>3.1097249999999996</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>6.7007469999999998</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>13.3141</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.92307692307692313</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21108,7 +21304,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21144,25 +21340,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>1083.8499999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>1083.8499999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.62728551336146277</v>
+      </c>
+      <c r="R157" s="7">
+        <v>15</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.54545454545454541</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.28657120450246804</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.012418508096138765</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.15938321723485724</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.076936384186003612</v>
+      </c>
+      <c r="X157" s="8">
+        <v>25.683336363636364</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>5.2855533333333335</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>4.2227272727272727</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>9.3424230000000001</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>16.278790909090908</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.90909090909090906</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21203,7 +21435,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21239,25 +21471,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2400.98</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2400.98</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>0.19173669398269699</v>
+      </c>
+      <c r="R158" s="7">
+        <v>23</v>
+      </c>
+      <c r="S158" s="6">
+        <v>0</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.26981211838499281</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.012905771809844313</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.044478921107214554</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.038233138135261434</v>
+      </c>
+      <c r="X158" s="8">
+        <v>26.655555555555555</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>8.3478260869565215</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>3.5250000000000004</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>11.803703000000001</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>18.74722222222222</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>-89.799999999999997</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22078,7 +22346,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22114,25 +22382,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>3150.0900000000001</v>
+      </c>
+      <c r="P165" s="5">
+        <v>3150.0900000000001</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.27337073837223391</v>
+      </c>
+      <c r="R165" s="7">
+        <v>39</v>
+      </c>
+      <c r="S165" s="6">
+        <v>0.14705882352941169</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.32867362519801019</v>
+      </c>
+      <c r="U165" s="6">
+        <v>0.0068478995838214141</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.025611173014104358</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.01404483681418626</v>
+      </c>
+      <c r="X165" s="8">
+        <v>18.404761904761905</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>3.5918794871794875</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.1992047619047619</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>5.2214280000000004</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>12.161109523809523</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-26.300000000000001</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
